--- a/testing_credentails.xlsx
+++ b/testing_credentails.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eyindia-my.sharepoint.com/personal/uday_kaushik_in_ey_com/Documents/e_drt_folder/credentails/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FQ932KZ\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{8FA3EBC1-6529-400D-A968-986447FB0514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9BA5DC3-DFC8-47A3-B81F-7DC0B588E8FF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E489928-6663-4970-9C71-AAF69F32BE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E57AE615-324F-477A-8AA7-A10342F25707}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E57AE615-324F-477A-8AA7-A10342F25707}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="live" sheetId="1" r:id="rId1"/>
+    <sheet name="test" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,23 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
-  <si>
-    <t>DRT login for delhi users</t>
-  </si>
-  <si>
-    <t>USER ID DRT Live</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
   <si>
     <t>PASSWORD</t>
   </si>
   <si>
-    <t>User ID DRT.20</t>
-  </si>
-  <si>
-    <t>User Name</t>
-  </si>
-  <si>
     <t>filingdrt1</t>
   </si>
   <si>
@@ -63,178 +51,89 @@
     <t>Admin@123</t>
   </si>
   <si>
-    <t>Filing login</t>
-  </si>
-  <si>
     <t>devendar</t>
   </si>
   <si>
     <t>Abc@1230</t>
   </si>
   <si>
-    <t>Dealing Hand (1st Level)</t>
-  </si>
-  <si>
     <t>soaswal</t>
   </si>
   <si>
-    <t>Dealing Hand (2nd Level)</t>
-  </si>
-  <si>
     <t>regskdubey</t>
   </si>
   <si>
-    <t>Dealing Hand (3rd Level)</t>
-  </si>
-  <si>
     <t>listrajeev</t>
   </si>
   <si>
     <t>Ddodrt1@2023</t>
   </si>
   <si>
-    <t>List login</t>
-  </si>
-  <si>
     <t>rajeevsinha</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>Raj@1230</t>
-    </r>
-  </si>
-  <si>
-    <t>Court Login</t>
-  </si>
-  <si>
     <t>rcdrt1</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>Ddodrt1@1230</t>
-    </r>
-  </si>
-  <si>
-    <t>Recovery Login</t>
-  </si>
-  <si>
     <t>dfsmis</t>
   </si>
   <si>
-    <t>MIS system</t>
-  </si>
-  <si>
-    <t>dratfillingdelhi</t>
-  </si>
-  <si>
-    <t>Module Name</t>
-  </si>
-  <si>
-    <t>UserName</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Filing Module</t>
-  </si>
-  <si>
     <t>dratfilingdelhi</t>
   </si>
   <si>
     <t>Drat@12345</t>
   </si>
   <si>
-    <t>Dealing Hand -1</t>
-  </si>
-  <si>
     <t>dratdelhidh</t>
   </si>
   <si>
     <t>Admin@1234</t>
   </si>
   <si>
-    <t>Dealing Hand (SO) -2</t>
-  </si>
-  <si>
     <t>dratdelhiso</t>
   </si>
   <si>
-    <t>Dealing Hand (Registrar) -3</t>
-  </si>
-  <si>
     <t>dratdelhirr</t>
   </si>
   <si>
     <t>Admin@12345</t>
   </si>
   <si>
-    <t>Listing</t>
-  </si>
-  <si>
     <t>dratdelhilisting</t>
   </si>
   <si>
     <t>List@2345</t>
   </si>
   <si>
-    <t>Court</t>
-  </si>
-  <si>
     <t>dratdelhicourt</t>
   </si>
   <si>
     <t>Court@123</t>
   </si>
   <si>
-    <t>Admin</t>
-  </si>
-  <si>
     <t>dratdelhiadmin</t>
   </si>
   <si>
-    <t>MIS</t>
-  </si>
-  <si>
     <t>dratdelhimis</t>
   </si>
   <si>
-    <t>DDO</t>
-  </si>
-  <si>
     <t>ddodratdelhi</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Sent request and save the response for all the URL's for both enviorment </t>
-  </si>
-  <si>
-    <t>2. Comparing both enviorment, forms and their field, visibility rules. Actually my report showing its present in form but its hidden because of depedency rule so we have to explore those part in both enviorment</t>
-  </si>
-  <si>
-    <t>2. Fill data in one to one field and check dependency rule, visibility rule.</t>
-  </si>
-  <si>
-    <t>3. Extract all the drop downs in testing enviorment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. On the basis of field and field type we have to create the dummy data and we have perfrom end to end testing. We have to verify data type, length, submission of data after clicking on submit. So create report in that format so that you will add dummy data in that sheet and perform ferther testing </t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Raj@1230</t>
+  </si>
+  <si>
+    <t>Ddodrt1@1230</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,18 +182,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri, sans-serif"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -309,7 +196,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -332,93 +219,34 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -756,341 +584,186 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5498B981-68C7-4E17-806A-C3BC16C74EE2}">
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="B8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="B9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="7"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+      <c r="B10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A11" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+      <c r="B11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C11" s="9"/>
+    </row>
+    <row r="12" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B12" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="C12" s="9"/>
+    </row>
+    <row r="13" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A13" s="11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
+      <c r="B13" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C13" s="9"/>
+    </row>
+    <row r="14" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A14" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="9"/>
+    </row>
+    <row r="15" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="9"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
+      <c r="C16" s="8"/>
+    </row>
+    <row r="17" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="B17" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" spans="1:5" ht="21.5" thickBot="1">
-      <c r="A13" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="1:5" ht="37.5" thickBot="1">
-      <c r="A14" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" spans="1:5" ht="37.5" thickBot="1">
-      <c r="A15" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16" spans="1:5" ht="37.5" thickBot="1">
-      <c r="A16" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" spans="1:5" ht="37.5" thickBot="1">
-      <c r="A17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18" spans="1:5" ht="37.5" thickBot="1">
-      <c r="A18" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" spans="1:5" ht="37.5" thickBot="1">
-      <c r="A19" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" spans="1:5" ht="37.5" thickBot="1">
-      <c r="A20" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5" ht="37.5" thickBot="1">
-      <c r="A21" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5" ht="37.5" thickBot="1">
-      <c r="A22" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+      <c r="B18" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{6B5BE48D-0AE9-4C3F-B487-54CDDFF13A87}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{6B29C811-9E0F-4D46-BB93-E138A383C115}"/>
-    <hyperlink ref="B6" r:id="rId3" xr:uid="{C83C6273-8B62-4938-B771-E457AF46AE44}"/>
-    <hyperlink ref="B7" r:id="rId4" xr:uid="{AB17A506-CC8E-4835-8AED-5123786E59C7}"/>
-    <hyperlink ref="B8" r:id="rId5" xr:uid="{84799FDF-39D1-4413-A239-4A78003DB0A8}"/>
-    <hyperlink ref="B9" r:id="rId6" xr:uid="{42711846-3EB6-4A15-889A-2F3B3F9D3051}"/>
-    <hyperlink ref="B10" r:id="rId7" xr:uid="{A6EA2172-5E39-4B19-A360-8E981C4DC649}"/>
-    <hyperlink ref="D4:D10" r:id="rId8" display="Admin@123" xr:uid="{FC90E086-D038-48AE-BB97-9A43FD036C42}"/>
-    <hyperlink ref="D11" r:id="rId9" xr:uid="{41C90586-772B-41DB-A259-DDB846872ED3}"/>
-    <hyperlink ref="C14" r:id="rId10" display="mailto:Drat@12345" xr:uid="{EBF85785-A83D-4288-AA6F-B0368FDC6796}"/>
-    <hyperlink ref="C20" r:id="rId11" display="mailto:Admin@12345" xr:uid="{BCCC5FC2-AE9A-4382-876D-E0E7CC390DC3}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{6B29C811-9E0F-4D46-BB93-E138A383C115}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{C83C6273-8B62-4938-B771-E457AF46AE44}"/>
+    <hyperlink ref="B6" r:id="rId3" xr:uid="{AB17A506-CC8E-4835-8AED-5123786E59C7}"/>
+    <hyperlink ref="B7" r:id="rId4" xr:uid="{84799FDF-39D1-4413-A239-4A78003DB0A8}"/>
+    <hyperlink ref="B8" r:id="rId5" xr:uid="{42711846-3EB6-4A15-889A-2F3B3F9D3051}"/>
+    <hyperlink ref="B9" r:id="rId6" xr:uid="{A6EA2172-5E39-4B19-A360-8E981C4DC649}"/>
+    <hyperlink ref="B10" r:id="rId7" display="mailto:Drat@12345" xr:uid="{EBF85785-A83D-4288-AA6F-B0368FDC6796}"/>
+    <hyperlink ref="B16" r:id="rId8" display="mailto:Admin@12345" xr:uid="{BCCC5FC2-AE9A-4382-876D-E0E7CC390DC3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1098,35 +771,163 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7859D82-FDA4-4B19-BE60-DC5E184AD058}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.81640625" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>58</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{E59BDCB4-B9E5-4D78-8878-24DC9CBD24F5}"/>
+    <hyperlink ref="B3:B9" r:id="rId2" display="Admin@123" xr:uid="{1E8377D5-9687-4A6D-9073-36797CD57472}"/>
+    <hyperlink ref="B10:B18" r:id="rId3" display="Admin@123" xr:uid="{264CB755-A90F-4CD9-8D25-AE9844D22306}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>